--- a/data/upload_template.xlsx
+++ b/data/upload_template.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakanjo\ProtonDrive\My files\forskningssektionen\projects-current\jeanette_melin-shiny\elderly_wellbeing\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeanettemelin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFF198E-F405-4982-8F6F-1F164160F318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D92078-CA89-3B49-BEFF-D070AD954A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$M$683</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Grupp</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>OPWELLS_1</t>
   </si>
@@ -77,7 +74,7 @@
     <t>Kön</t>
   </si>
   <si>
-    <t>Ålder</t>
+    <t>Åldersgrupp</t>
   </si>
 </sst>
 </file>
@@ -439,59 +436,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="13" width="15.85546875" customWidth="1"/>
+    <col min="1" max="12" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M683" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M683">
-      <sortCondition ref="A1:A683"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:O1" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/upload_template.xlsx
+++ b/data/upload_template.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeanettemelin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakanjo\ProtonDrive\My files\forskningssektionen\projects-current\jeanette_melin-shiny\elderly_wellbeing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D92078-CA89-3B49-BEFF-D070AD954A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFF198E-F405-4982-8F6F-1F164160F318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$M$683</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Grupp</t>
+  </si>
   <si>
     <t>OPWELLS_1</t>
   </si>
@@ -74,7 +77,7 @@
     <t>Kön</t>
   </si>
   <si>
-    <t>Åldersgrupp</t>
+    <t>Ålder</t>
   </si>
 </sst>
 </file>
@@ -436,52 +439,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="12" width="15.83203125" customWidth="1"/>
+    <col min="1" max="13" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}"/>
+  <autoFilter ref="A1:M683" xr:uid="{4D10C03F-0FB2-D64F-B9BC-63F645C94BEE}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M683">
+      <sortCondition ref="A1:A683"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
